--- a/tools/importer/reports/import-shop-home.report.xlsx
+++ b/tools/importer/reports/import-shop-home.report.xlsx
@@ -655,7 +655,7 @@
     <t>shop-home</t>
   </si>
   <si>
-    <t>2026-10-07T06:18:43.415Z</t>
+    <t>2026-10-07T07:01:01.218Z</t>
   </si>
   <si>
     <t>Shop | Home</t>
